--- a/public/outils/matrices/arbitrage-fiscal-nu-lmnp-sci-is.xlsx
+++ b/public/outils/matrices/arbitrage-fiscal-nu-lmnp-sci-is.xlsx
@@ -35,7 +35,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="650">
   <si>
-    <t>CorpusImmo  ·  corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
+    <t>CorpusImmo  ·  www.corpus.immo  ·  Estimer, comparer, décider. Sur les ventes réelles.</t>
   </si>
   <si>
     <t>Mode d'emploi</t>
@@ -167,7 +167,7 @@
     <t>Ce que vous faites</t>
   </si>
   <si>
-    <t>Fond bleu ciel, texte bleu nuit</t>
+    <t>Fond violet clair, texte violet sombre</t>
   </si>
   <si>
     <t>Saisie utilisateur</t>
@@ -185,7 +185,7 @@
     <t>Vous la lisez. Elle est verrouillée.</t>
   </si>
   <si>
-    <t>Fond presque blanc, texte bleu nuit en gras</t>
+    <t>Fond presque blanc, texte violet sombre en gras</t>
   </si>
   <si>
     <t>Résultat de bloc, chiffre clé</t>
@@ -194,7 +194,7 @@
     <t>Vous la lisez. C'est un chiffre à retenir.</t>
   </si>
   <si>
-    <t>Bandeau bleu nuit</t>
+    <t>Bandeau violet</t>
   </si>
   <si>
     <t>Titre de section, en-tête de tableau</t>
@@ -221,7 +221,7 @@
     <t>Rouge : corrigez la saisie indiquée dans le commentaire. Tant qu'un contrôle est rouge, le Comparateur reste entièrement vide, éligibilité et revente comprises : le classeur préfère ne rien afficher plutôt qu'un chiffre faux. Le Pluriannuel, lui, continue d'afficher le détail des années.</t>
   </si>
   <si>
-    <t>Les onglets sont protégés sans mot de passe pour éviter d'écraser une formule par erreur. Les cellules bleues restent modifiables et effaçables sans rien déverrouiller. Pour modifier une cellule blanche : onglet Révision, puis « Ôter la protection de la feuille ». Aucun mot de passe n'est demandé.</t>
+    <t>Les onglets sont protégés sans mot de passe pour éviter d'écraser une formule par erreur. Les cellules violettes restent modifiables et effaçables sans rien déverrouiller. Pour modifier une cellule blanche : onglet Révision, puis « Ôter la protection de la feuille ». Aucun mot de passe n'est demandé.</t>
   </si>
   <si>
     <t xml:space="preserve">  LA MARCHE À SUIVRE, ÉTAPE PAR ÉTAPE</t>
@@ -245,7 +245,7 @@
     <t>Le classeur arrive rempli d'un exemple. Gardez-le pour vous repérer, ou effacez vos données de projet avant de saisir votre dossier : les cinq premières plages ci-contre. Vérifiez surtout les saisies secondaires qui n'ont pas de raison d'être chez vous : travaux (Hypothèses!C10), mobilier (Hypothèses!C11), CFE (Hypothèses!C18), honoraires comptables (Hypothèses!C19 et Hypothèses!C20), autres revenus fonciers (Hypothèses!C37), prix de revente forcé (Hypothèses!C43). N'effacez jamais le mode d'acquisition (C8) ni les options C49:C57 : ce sont des listes, elles n'ont pas de valeur vide, et le classeur cesse de calculer dès qu'il en manque une. Ajustez-les une par une, ou gardez les valeurs livrées : achat à titre onéreux, meublé classique, distribution Non, frais immobilisés, rénovation énergétique Non, CSG déductible Non, terrain 15 %, bâti 30 ans, travaux 15 ans, mobilier 7 ans.</t>
   </si>
   <si>
-    <t>Une valeur résiduelle de l'exemple est l'erreur la plus probable d'un premier usage : 8 000 € de mobilier oubliés changent l'amortissement, la CFE et les cinq TRI. Pendant que vous effacez, les contrôles passent au rouge et le Comparateur se vide : c'est normal, tout revient dès que la saisie est complète. Les cellules bleues s'effacent avec la touche Suppr, sans rien déverrouiller.</t>
+    <t>Une valeur résiduelle de l'exemple est l'erreur la plus probable d'un premier usage : 8 000 € de mobilier oubliés changent l'amortissement, la CFE et les cinq TRI. Pendant que vous effacez, les contrôles passent au rouge et le Comparateur se vide : c'est normal, tout revient dès que la saisie est complète. Les cellules violettes s'effacent avec la touche Suppr, sans rien déverrouiller.</t>
   </si>
   <si>
     <t>1. Le bien</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">  LES DONNÉES À METTRE À JOUR, OÙ ET POURQUOI</t>
   </si>
   <si>
-    <t>Deux familles de données. Les benchmarks (barèmes fiscaux, plafonds, abattements de durée, repères de marché) changent avec la loi ou le marché, à date fixe, et se rafraîchissent depuis une source indiquée dans Paramètres. Les données de projet (prix, loyer, charges, financement, foyer, durée, options) sont propres à chaque dossier. L'architecture du classeur ne change pas quand les données changent : seules les cellules bleues bougent.</t>
+    <t>Deux familles de données. Les benchmarks (barèmes fiscaux, plafonds, abattements de durée, repères de marché) changent avec la loi ou le marché, à date fixe, et se rafraîchissent depuis une source indiquée dans Paramètres. Les données de projet (prix, loyer, charges, financement, foyer, durée, options) sont propres à chaque dossier. L'architecture du classeur ne change pas quand les données changent : seules les cellules violettes bougent.</t>
   </si>
   <si>
     <t>Les chiffres cités dans ce guide sont ceux du millésime 2026 : à chaque mise à jour d'une valeur de Paramètres, relisez les lignes du guide qui la citent, c'est-à-dire l'exemple guidé, le tableau ci-dessous et les erreurs qui faussent tout. Le guide est en texte : il ne se met pas à jour tout seul quand un barème bouge.</t>
@@ -692,7 +692,7 @@
     <t>Le même bien sous cinq régimes, sur toute la durée de détention, revente comprise. Saisissez ici, lisez le Comparateur.</t>
   </si>
   <si>
-    <t>Cellules bleues : à remplir.  Cellules blanches : calculées automatiquement.</t>
+    <t>Cellules violettes : à remplir.  Cellules blanches : calculées automatiquement.</t>
   </si>
   <si>
     <t xml:space="preserve">  LE BIEN</t>
@@ -2012,7 +2012,7 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -2032,19 +2032,19 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -2056,7 +2056,7 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FF0E1A33"/>
+      <color rgb="FF2F2650"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -2069,17 +2069,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E1A33"/>
+        <fgColor rgb="FF4B3D7C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F0FE"/>
+        <fgColor rgb="FFF1EEF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F9FF"/>
+        <fgColor rgb="FFF8F6FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -2488,6 +2488,204 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="10458450" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10458450" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="9763125" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9763125" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="12420600" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12420600" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="28813125" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28813125" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="13592175" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13592175" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8782050" y="311150"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8782050" y="311150"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3826,6 +4024,7 @@
     <mergeCell ref="C11:E11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4549,6 +4748,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
@@ -5459,6 +5659,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15679,6 +15880,7 @@
     <mergeCell ref="B98:AG98"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -17190,6 +17392,7 @@
     <mergeCell ref="B116:F116"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -17715,5 +17918,6 @@
     <mergeCell ref="B23:C23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>